--- a/src/src/main/resources/template/APM_EfficiencyEquipment_export_Template.xlsx
+++ b/src/src/main/resources/template/APM_EfficiencyEquipment_export_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\550004001\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gehealthcare-my.sharepoint.com/personal/550004001_gehealthcare_com/Documents/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49CEABA-5A25-47A6-ACA8-C5272EB113B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C49CEABA-5A25-47A6-ACA8-C5272EB113B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9398540D-9008-40D0-96B5-2886A6F5602A}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>设备名称</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>采购金额</t>
-  </si>
-  <si>
-    <t>检查人次</t>
   </si>
   <si>
     <t>收入</t>
@@ -74,13 +71,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -170,7 +167,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -448,22 +445,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.41796875" customWidth="1"/>
     <col min="2" max="2" width="12.5234375" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.234375" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" customWidth="1"/>
-    <col min="7" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.47265625" customWidth="1"/>
-    <col min="11" max="11" width="11.80859375" customWidth="1"/>
-    <col min="12" max="12" width="9.94921875" customWidth="1"/>
+    <col min="4" max="4" width="11.3125" customWidth="1"/>
+    <col min="5" max="5" width="13.20703125" customWidth="1"/>
+    <col min="6" max="6" width="10.26171875" customWidth="1"/>
+    <col min="7" max="8" width="12.15625" customWidth="1"/>
+    <col min="9" max="9" width="9.47265625" customWidth="1"/>
+    <col min="10" max="10" width="11.7890625" customWidth="1"/>
+    <col min="11" max="11" width="9.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.7" customHeight="1" thickBot="1">
+    <row r="1" spans="1:12" ht="26.7" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,11 +493,8 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
